--- a/proliferation_growth_curves/Incucyte_sheets/renamed/r2_replaced.xlsx
+++ b/proliferation_growth_curves/Incucyte_sheets/renamed/r2_replaced.xlsx
@@ -1254,7 +1254,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 = Lin 4 P13 LIN5-0B-b3</t>
+          <t>P17 LIN3-0A-b2 = Lin 4 P13 LIN5-0B-b3</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1918,92 +1918,92 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 1</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 2</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 3</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 3</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 4</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 4</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 5</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 5</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 6</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 6</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 7</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 7</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 8</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 8</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (A3), Image 9</t>
+          <t>P17 LIN3-0A-b2 (A3), Image 9</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 1</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 1</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 2</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 3</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 4</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 4</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 5</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 5</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 6</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 6</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 7</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 7</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 8</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 8</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>P13 LIN5-0B-b3 LIN3-0A-b2 (B3), Image 9</t>
+          <t>P17 LIN3-0A-b2 (B3), Image 9</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
